--- a/output/pdf_financials_xlsx/TIG.xlsx
+++ b/output/pdf_financials_xlsx/TIG.xlsx
@@ -6099,28 +6099,28 @@
         <v>3.792589</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.875178</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.862433</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.807217</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.684032999999999</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.684032999999999</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.534008999999999</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.534008999999999</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>10.052238</v>
       </c>
     </row>
     <row r="93">
@@ -6679,13 +6679,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.01412</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.015868</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001838</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -10253,7 +10253,11 @@
           <t>Reserve (note 7)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -33137,7 +33141,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -34335,7 +34343,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E260" s="5" t="n">
         <v>-0.01412</v>
       </c>

--- a/output/pdf_financials_xlsx/TIG.xlsx
+++ b/output/pdf_financials_xlsx/TIG.xlsx
@@ -2644,13 +2644,13 @@
         <v>0.002746</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.19348</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.002412</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.450115</v>
       </c>
     </row>
     <row r="35">
@@ -2760,13 +2760,13 @@
         <v>0.002746</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.19348</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.002412</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.450115</v>
       </c>
     </row>
     <row r="37">
@@ -3456,13 +3456,13 @@
         <v>0.019365</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.22265</v>
+        <v>0.02917</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.024694</v>
+        <v>0.022282</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.492681</v>
+        <v>0.042566</v>
       </c>
     </row>
     <row r="49">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/TIG.xlsx
+++ b/output/pdf_financials_xlsx/TIG.xlsx
@@ -7216,10 +7216,10 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -29389,7 +29389,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TIG.xlsx
+++ b/output/pdf_financials_xlsx/TIG.xlsx
@@ -1399,19 +1399,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.43445</v>
+        <v>-0.43445</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.603584</v>
+        <v>-0.603584</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.383213</v>
+        <v>-0.383213</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.402129</v>
+        <v>-0.402129</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.591372</v>
+        <v>-0.591372</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.082201</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
@@ -4818,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.082201</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0</v>
@@ -5050,7 +5050,7 @@
         <v>0.234414</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.217201</v>
+        <v>0.135</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0.661725</v>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.008914034017925307</v>
+        <v>0.03942209090473845</v>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.18678</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.031021</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>-0.019027</v>
@@ -8563,10 +8563,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.18678</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.031021</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>-0.019027</v>
@@ -11819,7 +11819,11 @@
           <t>Lease liabilities (note 8)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -31149,7 +31153,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -31842,7 +31850,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -32543,7 +32555,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -32745,7 +32761,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E244" s="5" t="n">
         <v>-0.43445</v>
       </c>
@@ -33349,7 +33369,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E250" s="5" t="n">
         <v>-0.18678</v>
       </c>
@@ -40549,7 +40573,11 @@
           <t>Deferred income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -41749,7 +41777,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -42749,7 +42781,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -43252,7 +43288,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -44757,7 +44797,11 @@
           <t>Future income tax recovery (Note 8)</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -45456,7 +45500,11 @@
           <t>Future income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E373" s="5" t="n">
         <v>0.43445</v>
       </c>
